--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박민지\Desktop\★ 구매 업무\◈ 보고 자료\09. 26년 사업계획\01. 월별 단가 영향 인자\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53687823-A809-4205-82E1-A597D9BC0533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E396284-BFA6-4249-9EED-5D3B4D64F185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F76B2AE-5DB7-4740-9054-E51EB5634948}"/>
   </bookViews>
@@ -344,7 +344,7 @@
     <numFmt numFmtId="178" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,7 +466,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -545,17 +545,20 @@
     <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -913,7 +916,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37802FCA-6AA8-48C0-AEEF-F959BD03128C}">
   <dimension ref="A1:AD13"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
@@ -926,49 +929,49 @@
     <col min="28" max="30" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="C1" s="28" t="s">
+    <row r="1" spans="1:30">
+      <c r="C1" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="C2" s="29">
+    <row r="2" spans="1:30">
+      <c r="C2" s="27">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46315</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26" t="s">
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+    </row>
+    <row r="3" spans="1:30">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -1136,7 +1139,7 @@
       <c r="AC4" s="20"/>
       <c r="AD4" s="20"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -1207,15 +1210,19 @@
         <v>79.45</v>
       </c>
       <c r="Y5" s="20">
-        <v>78.209999999999994</v>
-      </c>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
+        <v>76.75</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>88.75</v>
+      </c>
+      <c r="AA5" s="20">
+        <v>113.71</v>
+      </c>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20"/>
       <c r="AD5" s="20"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -1288,13 +1295,17 @@
       <c r="Y6" s="14">
         <v>807.13</v>
       </c>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
+      <c r="Z6" s="14">
+        <v>795.62</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>908.23</v>
+      </c>
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -1367,13 +1378,17 @@
       <c r="Y7" s="14">
         <v>876</v>
       </c>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
+      <c r="Z7" s="30">
+        <v>1005</v>
+      </c>
+      <c r="AA7" s="30">
+        <v>1172.5</v>
+      </c>
       <c r="AB7" s="14"/>
       <c r="AC7" s="14"/>
       <c r="AD7" s="14"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30">
       <c r="A8" t="s">
         <v>77</v>
       </c>
@@ -1449,13 +1464,17 @@
       <c r="Y8" s="14">
         <v>174.89</v>
       </c>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
+      <c r="Z8" s="14">
+        <v>184.7</v>
+      </c>
+      <c r="AA8" s="14">
+        <v>205.48</v>
+      </c>
       <c r="AB8" s="14"/>
       <c r="AC8" s="14"/>
       <c r="AD8" s="14"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -1531,13 +1550,17 @@
       <c r="Y9" s="20">
         <v>760</v>
       </c>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
+      <c r="Z9" s="20">
+        <v>735</v>
+      </c>
+      <c r="AA9" s="20">
+        <v>735</v>
+      </c>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20"/>
       <c r="AD9" s="20"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -1613,13 +1636,17 @@
       <c r="Y10" s="20">
         <v>83.8</v>
       </c>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
+      <c r="Z10" s="20">
+        <v>91.2</v>
+      </c>
+      <c r="AA10" s="20">
+        <v>92.9</v>
+      </c>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20"/>
       <c r="AD10" s="20"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30">
       <c r="B11" s="24">
         <v>8</v>
       </c>
@@ -1686,13 +1713,17 @@
       <c r="Y11" s="14">
         <v>1441.1</v>
       </c>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
+      <c r="Z11" s="14">
+        <v>1406.3</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>1359</v>
+      </c>
       <c r="AB11" s="14"/>
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30">
       <c r="B12" s="24">
         <v>9</v>
       </c>
@@ -1759,13 +1790,17 @@
       <c r="Y12" s="14">
         <v>1709.78</v>
       </c>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
+      <c r="Z12" s="14">
+        <v>1629.78</v>
+      </c>
+      <c r="AA12" s="14">
+        <v>1567.13</v>
+      </c>
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30">
       <c r="B13" s="24">
         <v>10</v>
       </c>
@@ -1832,8 +1867,12 @@
       <c r="Y13" s="14">
         <v>921.46</v>
       </c>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
+      <c r="Z13" s="14">
+        <v>885.63</v>
+      </c>
+      <c r="AA13" s="14">
+        <v>869.52</v>
+      </c>
       <c r="AB13" s="14"/>
       <c r="AC13" s="14"/>
       <c r="AD13" s="14"/>
@@ -1852,7 +1891,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED04673-265D-4FFA-BAC0-BC27D5C626CF}">
   <dimension ref="B2:I16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.375" bestFit="1" customWidth="1"/>
@@ -1863,12 +1902,12 @@
     <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9">
       <c r="B2" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9">
       <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
@@ -1894,7 +1933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1920,7 +1959,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9">
       <c r="B5" s="2">
         <v>2</v>
       </c>
@@ -1946,7 +1985,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9">
       <c r="B6" s="2">
         <v>3</v>
       </c>
@@ -1972,7 +2011,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9">
       <c r="B7" s="2">
         <v>4</v>
       </c>
@@ -1998,7 +2037,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9">
       <c r="B8" s="2">
         <v>5</v>
       </c>
@@ -2024,7 +2063,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9">
       <c r="B9" s="2">
         <v>6</v>
       </c>
@@ -2050,7 +2089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9">
       <c r="B10" s="2">
         <v>7</v>
       </c>
@@ -2076,13 +2115,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9">
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9">
       <c r="B12" s="11" t="s">
         <v>51</v>
       </c>
@@ -2090,7 +2129,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9">
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
@@ -2103,14 +2142,14 @@
       <c r="E13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9">
       <c r="B14" s="2">
         <v>1</v>
       </c>
@@ -2121,12 +2160,12 @@
         <v>54</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="27"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:9">
       <c r="B15" s="2">
         <v>2</v>
       </c>
@@ -2137,12 +2176,12 @@
         <v>54</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="27"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" spans="2:9">
       <c r="B16" s="2">
         <v>3</v>
       </c>
@@ -2155,10 +2194,10 @@
       <c r="E16" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="27"/>
+      <c r="G16" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">
